--- a/docs/sample-output/09-tiny-home-community/proforma.xlsx
+++ b/docs/sample-output/09-tiny-home-community/proforma.xlsx
@@ -267,7 +267,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 1 at 44.26% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 1 at 51.51% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   Cedar Pines tiny home community · 5-Year Before-Tax</t>
@@ -1055,7 +1055,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>3385833.89</v>
+        <v>3314792.62</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1063,7 +1063,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="8">
-        <v>0.0805379143983936</v>
+        <v>0.0822639698045424</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1071,7 +1071,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="7">
-        <v>1207049.781785</v>
+        <v>1181723.56903</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1087,7 +1087,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>0.20878622444268974</v>
+        <v>0.2207868432207924</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1095,7 +1095,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="9">
-        <v>2.3638282965780113</v>
+        <v>2.465707371886607</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1111,7 +1111,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="8">
-        <v>0.4426201750414763</v>
+        <v>0.5151345758695919</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1126,7 +1126,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="7">
-        <v>3385833.89</v>
+        <v>3314792.62</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1142,7 +1142,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="7">
-        <v>22007.920285</v>
+        <v>21546.15203</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="7">
-        <v>3385833.89</v>
+        <v>3314792.62</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1158,7 +1158,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="7">
-        <v>-2200792.0285</v>
+        <v>-2154615.203</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1166,7 +1166,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>1207049.781785</v>
+        <v>1181723.56903</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1174,7 +1174,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>7.425074320175439</v>
+        <v>7.269282061403509</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1182,7 +1182,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="7">
-        <v>84645.84725</v>
+        <v>82869.8155</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1197,7 +1197,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="7">
-        <v>2200792.0285</v>
+        <v>2154615.203</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1229,7 +1229,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="14">
-        <v>14859.905382800032</v>
+        <v>14548.11615014103</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1237,7 +1237,7 @@
         <v>44</v>
       </c>
       <c r="B37" s="7">
-        <v>178318.8645936004</v>
+        <v>174577.39380169235</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1472,19 +1472,19 @@
         <v>61</v>
       </c>
       <c r="B13" s="17">
-        <v>-178318.8645936004</v>
+        <v>-174577.39380169235</v>
       </c>
       <c r="C13" s="17">
-        <v>-178318.8645936004</v>
+        <v>-174577.39380169235</v>
       </c>
       <c r="D13" s="17">
-        <v>-178318.8645936004</v>
+        <v>-174577.39380169235</v>
       </c>
       <c r="E13" s="17">
-        <v>-178318.8645936004</v>
+        <v>-174577.39380169235</v>
       </c>
       <c r="F13" s="17">
-        <v>-178318.8645936004</v>
+        <v>-174577.39380169235</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1492,19 +1492,19 @@
         <v>62</v>
       </c>
       <c r="B14" s="19">
-        <v>94369.13540639961</v>
+        <v>98110.60619830765</v>
       </c>
       <c r="C14" s="19">
-        <v>102549.77540639963</v>
+        <v>106291.24619830766</v>
       </c>
       <c r="D14" s="19">
-        <v>110975.83460639964</v>
+        <v>114717.30539830768</v>
       </c>
       <c r="E14" s="19">
-        <v>119654.67558239959</v>
+        <v>123396.14637430763</v>
       </c>
       <c r="F14" s="19">
-        <v>128593.88178767962</v>
+        <v>132335.35257958766</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1648,19 +1648,19 @@
         <v>69</v>
       </c>
       <c r="B9" s="17">
-        <v>-2164454.767923784</v>
+        <v>-2119040.3676411817</v>
       </c>
       <c r="C9" s="17">
-        <v>-2125683.9337100806</v>
+        <v>-2081083.0196736983</v>
       </c>
       <c r="D9" s="17">
-        <v>-2084316.544925401</v>
+        <v>-2040583.597815727</v>
       </c>
       <c r="E9" s="17">
-        <v>-2040178.7055013026</v>
+        <v>-1997371.8546708955</v>
       </c>
       <c r="F9" s="17">
-        <v>-1993084.8732275811</v>
+        <v>-1951266.141059396</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1668,19 +1668,19 @@
         <v>70</v>
       </c>
       <c r="B10" s="19">
-        <v>1646945.232076216</v>
+        <v>1692359.6323588183</v>
       </c>
       <c r="C10" s="19">
-        <v>1800666.0662899194</v>
+        <v>1845266.9803263017</v>
       </c>
       <c r="D10" s="19">
-        <v>1959833.455074599</v>
+        <v>2003566.402184273</v>
       </c>
       <c r="E10" s="19">
-        <v>2124621.2944986974</v>
+        <v>2167428.1453291047</v>
       </c>
       <c r="F10" s="19">
-        <v>2297115.1267724186</v>
+        <v>2338933.858940604</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1718,19 +1718,19 @@
         <v>72</v>
       </c>
       <c r="B13" s="22">
-        <v>0.5394952063618604</v>
+        <v>0.5281755652146515</v>
       </c>
       <c r="C13" s="22">
-        <v>0.5143198484660249</v>
+        <v>0.5035284344722232</v>
       </c>
       <c r="D13" s="22">
-        <v>0.4896209877673012</v>
+        <v>0.47934780310446956</v>
       </c>
       <c r="E13" s="22">
-        <v>0.4653692302694577</v>
+        <v>0.4556048938574123</v>
       </c>
       <c r="F13" s="22">
-        <v>0.44133854588741833</v>
+        <v>0.43207841918941453</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1738,19 +1738,19 @@
         <v>73</v>
       </c>
       <c r="B14" s="23">
-        <v>1.5292156588225965</v>
+        <v>1.5619891789068314</v>
       </c>
       <c r="C14" s="23">
-        <v>1.5750921285872745</v>
+        <v>1.6088488542740365</v>
       </c>
       <c r="D14" s="23">
-        <v>1.6223448924448929</v>
+        <v>1.6571143199022578</v>
       </c>
       <c r="E14" s="23">
-        <v>1.6710152392182394</v>
+        <v>1.7068277494993251</v>
       </c>
       <c r="F14" s="23">
-        <v>1.7211456963947867</v>
+        <v>1.758032581984305</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1758,19 +1758,19 @@
         <v>74</v>
       </c>
       <c r="B15" s="22">
-        <v>0.1239044836898363</v>
+        <v>0.12655995354544983</v>
       </c>
       <c r="C15" s="22">
-        <v>0.1276216182005314</v>
+        <v>0.13035675215181333</v>
       </c>
       <c r="D15" s="22">
-        <v>0.13145026674654733</v>
+        <v>0.13426745471636775</v>
       </c>
       <c r="E15" s="22">
-        <v>0.13539377474894373</v>
+        <v>0.13829547835785877</v>
       </c>
       <c r="F15" s="22">
-        <v>0.13945558799141208</v>
+        <v>0.14244434270859455</v>
       </c>
     </row>
   </sheetData>
@@ -1846,19 +1846,19 @@
         <v>76</v>
       </c>
       <c r="B5" s="22">
-        <v>0.07818164323500011</v>
+        <v>0.08302331337847503</v>
       </c>
       <c r="C5" s="22">
-        <v>0.0849590273358467</v>
+        <v>0.08994594758362588</v>
       </c>
       <c r="D5" s="22">
-        <v>0.0919397329597187</v>
+        <v>0.09707626081493125</v>
       </c>
       <c r="E5" s="22">
-        <v>0.0991298597523068</v>
+        <v>0.10442048344317573</v>
       </c>
       <c r="F5" s="22">
-        <v>0.10653569034867262</v>
+        <v>0.11198503275026761</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1866,19 +1866,19 @@
         <v>77</v>
       </c>
       <c r="B6" s="22">
-        <v>0.057299498227657196</v>
+        <v>0.057972669828788494</v>
       </c>
       <c r="C6" s="22">
-        <v>0.05695102347193809</v>
+        <v>0.057602096244908696</v>
       </c>
       <c r="D6" s="22">
-        <v>0.05662513532415205</v>
+        <v>0.05725655275175494</v>
       </c>
       <c r="E6" s="22">
-        <v>0.05631811932424033</v>
+        <v>0.05693205868911102</v>
       </c>
       <c r="F6" s="22">
-        <v>0.055980599443599316</v>
+        <v>0.05657934792543796</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1886,19 +1886,19 @@
         <v>78</v>
       </c>
       <c r="B7" s="24">
-        <v>1.4426201750416114</v>
+        <v>1.515134575869386</v>
       </c>
       <c r="C7" s="24">
-        <v>1.6549317246457436</v>
+        <v>1.7344740228929825</v>
       </c>
       <c r="D7" s="24">
-        <v>1.878736266486253</v>
+        <v>1.9655066725001837</v>
       </c>
       <c r="E7" s="24">
-        <v>2.114387288754665</v>
+        <v>2.2085905011107365</v>
       </c>
       <c r="F7" s="24">
-        <v>2.3638282965780113</v>
+        <v>2.465707371886607</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1906,19 +1906,19 @@
         <v>79</v>
       </c>
       <c r="B8" s="22">
-        <v>0.20622810589232624</v>
+        <v>0.2320794897873753</v>
       </c>
       <c r="C8" s="22">
-        <v>0.1557133124667583</v>
+        <v>0.16848159122906314</v>
       </c>
       <c r="D8" s="22">
-        <v>0.13932943301884498</v>
+        <v>0.1480106927521852</v>
       </c>
       <c r="E8" s="22">
-        <v>0.13120807427359077</v>
+        <v>0.1378995456881122</v>
       </c>
       <c r="F8" s="22">
-        <v>0.12643102297575753</v>
+        <v>0.13194854536142353</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1946,19 +1946,19 @@
         <v>81</v>
       </c>
       <c r="B10" s="25">
-        <v>0.4426201750414763</v>
+        <v>0.5151345758695919</v>
       </c>
       <c r="C10" s="25">
-        <v>0.29538623820785487</v>
+        <v>0.3272697704707003</v>
       </c>
       <c r="D10" s="25">
-        <v>0.24791523238743066</v>
+        <v>0.26829948914848706</v>
       </c>
       <c r="E10" s="25">
-        <v>0.22369470999401786</v>
+        <v>0.23874150315816392</v>
       </c>
       <c r="F10" s="25">
-        <v>0.20878622444268974</v>
+        <v>0.2207868432207924</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1966,19 +1966,19 @@
         <v>82</v>
       </c>
       <c r="B11" s="22">
-        <v>0.2364</v>
+        <v>0.28300000000000003</v>
       </c>
       <c r="C11" s="22">
-        <v>0.1397</v>
+        <v>0.15879999999999997</v>
       </c>
       <c r="D11" s="22">
-        <v>0.1086</v>
+        <v>0.12029999999999999</v>
       </c>
       <c r="E11" s="22">
-        <v>0.0925</v>
+        <v>0.1008</v>
       </c>
       <c r="F11" s="22">
-        <v>0.0824</v>
+        <v>0.0889</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2072,19 +2072,19 @@
         <v>19</v>
       </c>
       <c r="B6" s="19">
-        <v>3047251</v>
+        <v>2983313</v>
       </c>
       <c r="C6" s="19">
-        <v>3216542</v>
+        <v>3149053</v>
       </c>
       <c r="D6" s="19">
-        <v>3385834</v>
+        <v>3314793</v>
       </c>
       <c r="E6" s="19">
-        <v>3555126</v>
+        <v>3480532</v>
       </c>
       <c r="F6" s="19">
-        <v>3724417</v>
+        <v>3646272</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2092,19 +2092,19 @@
         <v>20</v>
       </c>
       <c r="B7" s="22">
-        <v>0.08948655689997312</v>
+        <v>0.09140442186254007</v>
       </c>
       <c r="C7" s="22">
-        <v>0.08477675715100254</v>
+        <v>0.08659365212335264</v>
       </c>
       <c r="D7" s="22">
-        <v>0.08053791178185345</v>
+        <v>0.0822639603739962</v>
       </c>
       <c r="E7" s="22">
-        <v>0.07670276665299626</v>
+        <v>0.07834664355908809</v>
       </c>
       <c r="F7" s="22">
-        <v>0.07321629130143054</v>
+        <v>0.07478542467484597</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2112,19 +2112,19 @@
         <v>91</v>
       </c>
       <c r="B8" s="17">
-        <v>1980713.1500000001</v>
+        <v>1939153.45</v>
       </c>
       <c r="C8" s="17">
-        <v>2090752.3</v>
+        <v>2046884.4500000002</v>
       </c>
       <c r="D8" s="17">
-        <v>2200792.1</v>
+        <v>2154615.45</v>
       </c>
       <c r="E8" s="17">
-        <v>2310831.9</v>
+        <v>2262345.8000000003</v>
       </c>
       <c r="F8" s="17">
-        <v>2420871.0500000003</v>
+        <v>2370076.8000000003</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2132,19 +2132,19 @@
         <v>21</v>
       </c>
       <c r="B9" s="17">
-        <v>1086344.9815</v>
+        <v>1063551.0845</v>
       </c>
       <c r="C9" s="17">
-        <v>1146697.223</v>
+        <v>1122637.3945</v>
       </c>
       <c r="D9" s="17">
-        <v>1207049.821</v>
+        <v>1181723.7045</v>
       </c>
       <c r="E9" s="17">
-        <v>1267402.4190000002</v>
+        <v>1240809.6579999998</v>
       </c>
       <c r="F9" s="17">
-        <v>1327754.6604999998</v>
+        <v>1299895.9679999999</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2152,19 +2152,19 @@
         <v>92</v>
       </c>
       <c r="B10" s="22">
-        <v>0.08948655689997312</v>
+        <v>0.09140442186254007</v>
       </c>
       <c r="C10" s="22">
-        <v>0.08477675715100254</v>
+        <v>0.08659365212335264</v>
       </c>
       <c r="D10" s="22">
-        <v>0.08053791178185345</v>
+        <v>0.0822639603739962</v>
       </c>
       <c r="E10" s="22">
-        <v>0.07670276665299626</v>
+        <v>0.07834664355908809</v>
       </c>
       <c r="F10" s="22">
-        <v>0.07321629130143054</v>
+        <v>0.07478542467484597</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2172,19 +2172,19 @@
         <v>93</v>
       </c>
       <c r="B11" s="22">
-        <v>0.09217115360697233</v>
+        <v>0.09414655451841628</v>
       </c>
       <c r="C11" s="22">
-        <v>0.08732005986553262</v>
+        <v>0.08919146168705322</v>
       </c>
       <c r="D11" s="22">
-        <v>0.08295404913530906</v>
+        <v>0.08473187918521609</v>
       </c>
       <c r="E11" s="22">
-        <v>0.07900384965258615</v>
+        <v>0.08069704286586074</v>
       </c>
       <c r="F11" s="22">
-        <v>0.07541278004047346</v>
+        <v>0.07702898741509136</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2192,19 +2192,19 @@
         <v>94</v>
       </c>
       <c r="B12" s="22">
-        <v>0.09493628821518149</v>
+        <v>0.09697095115396877</v>
       </c>
       <c r="C12" s="22">
-        <v>0.0899396616614986</v>
+        <v>0.09186720553766482</v>
       </c>
       <c r="D12" s="22">
-        <v>0.08544267060936833</v>
+        <v>0.08727383556077259</v>
       </c>
       <c r="E12" s="22">
-        <v>0.08137396514216375</v>
+        <v>0.08311795415183656</v>
       </c>
       <c r="F12" s="22">
-        <v>0.07767516344168766</v>
+        <v>0.0793398570375441</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2212,19 +2212,19 @@
         <v>95</v>
       </c>
       <c r="B13" s="22">
-        <v>0.09778437686163692</v>
+        <v>0.09988007968858781</v>
       </c>
       <c r="C13" s="22">
-        <v>0.09263785151134354</v>
+        <v>0.09462322170379475</v>
       </c>
       <c r="D13" s="22">
-        <v>0.08800595072764937</v>
+        <v>0.08989205062759574</v>
       </c>
       <c r="E13" s="22">
-        <v>0.08381518409642864</v>
+        <v>0.08561149277639164</v>
       </c>
       <c r="F13" s="22">
-        <v>0.08000541834493828</v>
+        <v>0.08172005274867042</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2232,19 +2232,19 @@
         <v>96</v>
       </c>
       <c r="B14" s="22">
-        <v>0.10071790816748605</v>
+        <v>0.10287648207924546</v>
       </c>
       <c r="C14" s="22">
-        <v>0.09541698705668386</v>
+        <v>0.09746191835490861</v>
       </c>
       <c r="D14" s="22">
-        <v>0.09064612924947886</v>
+        <v>0.09258881214642363</v>
       </c>
       <c r="E14" s="22">
-        <v>0.08632963961932151</v>
+        <v>0.08817983755968341</v>
       </c>
       <c r="F14" s="22">
-        <v>0.08240558089528643</v>
+        <v>0.08417165433113054</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2252,19 +2252,19 @@
         <v>97</v>
       </c>
       <c r="B15" s="22">
-        <v>0.1032830247261068</v>
+        <v>0.10866273009095095</v>
       </c>
       <c r="C15" s="22">
-        <v>0.09007180523390321</v>
+        <v>0.09516828481973796</v>
       </c>
       <c r="D15" s="22">
-        <v>0.07818163589547655</v>
+        <v>0.08302328692533001</v>
       </c>
       <c r="E15" s="22">
-        <v>0.0674238655480511</v>
+        <v>0.07203502096485845</v>
       </c>
       <c r="F15" s="22">
-        <v>0.057644131041555344</v>
+        <v>0.062045627180168095</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2272,19 +2272,19 @@
         <v>98</v>
       </c>
       <c r="B16" s="22">
-        <v>0.1108134502716866</v>
+        <v>0.11635454679747607</v>
       </c>
       <c r="C16" s="22">
-        <v>0.0972058941947169</v>
+        <v>0.1024552681681267</v>
       </c>
       <c r="D16" s="22">
-        <v>0.08495901977613744</v>
+        <v>0.0899459203368865</v>
       </c>
       <c r="E16" s="22">
-        <v>0.07387851631828923</v>
+        <v>0.0786280063976008</v>
       </c>
       <c r="F16" s="22">
-        <v>0.0638053897765986</v>
+        <v>0.06833893079936973</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2292,19 +2292,19 @@
         <v>99</v>
       </c>
       <c r="B17" s="22">
-        <v>0.1185697885836338</v>
+        <v>0.12427711800519696</v>
       </c>
       <c r="C17" s="22">
-        <v>0.10455400582435499</v>
+        <v>0.1099608610169671</v>
       </c>
       <c r="D17" s="22">
-        <v>0.09193972517321816</v>
+        <v>0.0970762327507897</v>
       </c>
       <c r="E17" s="22">
-        <v>0.0805268066116345</v>
+        <v>0.08541878139332543</v>
       </c>
       <c r="F17" s="22">
-        <v>0.07015148627369315</v>
+        <v>0.07482103352714742</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2312,19 +2312,19 @@
         <v>100</v>
       </c>
       <c r="B18" s="22">
-        <v>0.12655881704493935</v>
+        <v>0.1324373663491494</v>
       </c>
       <c r="C18" s="22">
-        <v>0.11212256080288217</v>
+        <v>0.11769162165127264</v>
       </c>
       <c r="D18" s="22">
-        <v>0.09912985173221125</v>
+        <v>0.10442045453710994</v>
       </c>
       <c r="E18" s="22">
-        <v>0.08737454561378007</v>
+        <v>0.09241327963892172</v>
       </c>
       <c r="F18" s="22">
-        <v>0.07668796566570049</v>
+        <v>0.08149759933675839</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2332,19 +2332,19 @@
         <v>101</v>
       </c>
       <c r="B19" s="22">
-        <v>0.13478751636008413</v>
+        <v>0.1408424221434205</v>
       </c>
       <c r="C19" s="22">
-        <v>0.11991817243076526</v>
+        <v>0.12565430510460743</v>
       </c>
       <c r="D19" s="22">
-        <v>0.10653568208797419</v>
+        <v>0.11198500297701984</v>
       </c>
       <c r="E19" s="22">
-        <v>0.09442771678599009</v>
+        <v>0.09961761283188598</v>
       </c>
       <c r="F19" s="22">
-        <v>0.08342053943946812</v>
+        <v>0.08837446212065775</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2352,19 +2352,19 @@
         <v>102</v>
       </c>
       <c r="B20" s="22">
-        <v>0.34025323151889586</v>
+        <v>0.3689773751528388</v>
       </c>
       <c r="C20" s="22">
-        <v>0.2697138728483829</v>
+        <v>0.2969257741930129</v>
       </c>
       <c r="D20" s="22">
-        <v>0.20622806670394003</v>
+        <v>0.23207934854442452</v>
       </c>
       <c r="E20" s="22">
-        <v>0.14878853801496972</v>
+        <v>0.17340912251337065</v>
       </c>
       <c r="F20" s="22">
-        <v>0.09657108750187783</v>
+        <v>0.1200722271954058</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2372,19 +2372,19 @@
         <v>103</v>
       </c>
       <c r="B21" s="22">
-        <v>0.22060990078724121</v>
+        <v>0.23412098761046285</v>
       </c>
       <c r="C21" s="22">
-        <v>0.1868494248946702</v>
+        <v>0.19997363333503515</v>
       </c>
       <c r="D21" s="22">
-        <v>0.15571329301516035</v>
+        <v>0.16848152180941367</v>
       </c>
       <c r="E21" s="22">
-        <v>0.1268797676237598</v>
+        <v>0.13931905361113744</v>
       </c>
       <c r="F21" s="22">
-        <v>0.10007964196881466</v>
+        <v>0.11221332741620821</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2392,19 +2392,19 @@
         <v>104</v>
       </c>
       <c r="B22" s="22">
-        <v>0.18319555124705222</v>
+        <v>0.1922498485133531</v>
       </c>
       <c r="C22" s="22">
-        <v>0.16045493146544426</v>
+        <v>0.169315284416037</v>
       </c>
       <c r="D22" s="22">
-        <v>0.13932941977429136</v>
+        <v>0.1480106456217113</v>
       </c>
       <c r="E22" s="22">
-        <v>0.11962999357521661</v>
+        <v>0.128145082965133</v>
       </c>
       <c r="F22" s="22">
-        <v>0.10119760984229065</v>
+        <v>0.10955770336447274</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2412,19 +2412,19 @@
         <v>105</v>
       </c>
       <c r="B23" s="22">
-        <v>0.16493906402021666</v>
+        <v>0.17187702621063933</v>
       </c>
       <c r="C23" s="22">
-        <v>0.1474775367313021</v>
+        <v>0.15428727506257417</v>
       </c>
       <c r="D23" s="22">
-        <v>0.13120806405856217</v>
+        <v>0.13789950938261603</v>
       </c>
       <c r="E23" s="22">
-        <v>0.115993344940203</v>
+        <v>0.12257517955809812</v>
       </c>
       <c r="F23" s="22">
-        <v>0.10171769151905558</v>
+        <v>0.1081973075541395</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2432,19 +2432,19 @@
         <v>106</v>
       </c>
       <c r="B24" s="22">
-        <v>0.15421607936012077</v>
+        <v>0.15992270548481957</v>
       </c>
       <c r="C24" s="22">
-        <v>0.13984125618349313</v>
+        <v>0.14544937437593136</v>
       </c>
       <c r="D24" s="22">
-        <v>0.12643101455035038</v>
+        <v>0.13194851543299047</v>
       </c>
       <c r="E24" s="22">
-        <v>0.11387461769672666</v>
+        <v>0.11930837144075998</v>
       </c>
       <c r="F24" s="22">
-        <v>0.10207878043418869</v>
+        <v>0.10743460456954491</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2452,19 +2452,19 @@
         <v>107</v>
       </c>
       <c r="B25" s="22">
-        <v>0.8185672314992376</v>
+        <v>0.899139864413053</v>
       </c>
       <c r="C25" s="22">
-        <v>0.6207008677663421</v>
+        <v>0.6970315868251618</v>
       </c>
       <c r="D25" s="22">
-        <v>0.4426200651165767</v>
+        <v>0.5151341796769627</v>
       </c>
       <c r="E25" s="22">
-        <v>0.2814993675327699</v>
+        <v>0.3505613156345021</v>
       </c>
       <c r="F25" s="22">
-        <v>0.13502685557341043</v>
+        <v>0.2009487060467312</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2472,19 +2472,19 @@
         <v>108</v>
       </c>
       <c r="B26" s="22">
-        <v>0.454031744347785</v>
+        <v>0.48610831030614515</v>
       </c>
       <c r="C26" s="22">
-        <v>0.37252523906934215</v>
+        <v>0.40445405529649864</v>
       </c>
       <c r="D26" s="22">
-        <v>0.2953861893549672</v>
+        <v>0.3272695981024744</v>
       </c>
       <c r="E26" s="22">
-        <v>0.22194934927057475</v>
+        <v>0.253889840589339</v>
       </c>
       <c r="F26" s="22">
-        <v>0.15163722495914606</v>
+        <v>0.18373912976241064</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2492,19 +2492,19 @@
         <v>109</v>
       </c>
       <c r="B27" s="22">
-        <v>0.3484132739223351</v>
+        <v>0.368462747242264</v>
       </c>
       <c r="C27" s="22">
-        <v>0.2970677892961009</v>
+        <v>0.317251516352659</v>
       </c>
       <c r="D27" s="22">
-        <v>0.24791520107885398</v>
+        <v>0.26829937921068187</v>
       </c>
       <c r="E27" s="22">
-        <v>0.20058292331366906</v>
+        <v>0.22123625470131136</v>
       </c>
       <c r="F27" s="22">
-        <v>0.15474160998134173</v>
+        <v>0.17573641782951177</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2512,19 +2512,19 @@
         <v>110</v>
       </c>
       <c r="B28" s="22">
-        <v>0.29774640614347203</v>
+        <v>0.3124812568764339</v>
       </c>
       <c r="C28" s="22">
-        <v>0.2599536800058164</v>
+        <v>0.27481992861687543</v>
       </c>
       <c r="D28" s="22">
-        <v>0.22369468687259814</v>
+        <v>0.2387414220437789</v>
       </c>
       <c r="E28" s="22">
-        <v>0.18870274788654437</v>
+        <v>0.20398054866364182</v>
       </c>
       <c r="F28" s="22">
-        <v>0.15474288426921495</v>
+        <v>0.17030455400675387</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2532,19 +2532,19 @@
         <v>111</v>
       </c>
       <c r="B29" s="22">
-        <v>0.2679025099971611</v>
+        <v>0.2796819049122262</v>
       </c>
       <c r="C29" s="22">
-        <v>0.23771473680644645</v>
+        <v>0.24958522871055155</v>
       </c>
       <c r="D29" s="22">
-        <v>0.2087862060069432</v>
+        <v>0.22078677851148415</v>
       </c>
       <c r="E29" s="22">
-        <v>0.18090247189859682</v>
+        <v>0.19307246535843858</v>
       </c>
       <c r="F29" s="22">
-        <v>0.153876601092079</v>
+        <v>0.16625622908615476</v>
       </c>
     </row>
   </sheetData>
